--- a/features/security/sandbox/batch3/security_batch3_v01.xlsx
+++ b/features/security/sandbox/batch3/security_batch3_v01.xlsx
@@ -10494,7 +10494,8 @@
           <t xml:space="preserve">verification: document review (R-SEC23; upstream DR-a/i/r pending)
 source: 037 SWE1-LOGENC-004 Requirement Description and Verification Criteria
 sibling axis: symmetric algorithm; rule R-SEC23(b) VC THEN 3.1
-channel_feasible: N/N</t>
+channel_feasible: N/N
+conflict: 376/509/511 vs 510 vs 514 — key strength; unresolved per CCVR Mapping notes row 14</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10632,8 @@
           <t xml:space="preserve">verification: document review (R-SEC23; upstream DR-a/i/r pending)
 source: 037 SWE1-LOGENC-004 Requirement Description and Verification Criteria
 sibling axis: key generation source; rule R-SEC23(b) VC trailing sentence (independent requirement outside THEN)
-channel_feasible: N/N</t>
+channel_feasible: N/N
+conflict: 376/509/511 vs 510 vs 514 — key strength; unresolved per CCVR Mapping notes row 14</t>
         </is>
       </c>
     </row>

--- a/features/security/sandbox/batch3/security_batch3_v01.xlsx
+++ b/features/security/sandbox/batch3/security_batch3_v01.xlsx
@@ -7940,7 +7940,9 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0001</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8077,7 +8079,9 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0019</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8214,7 +8218,24 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUONLINE</t>
+          <t xml:space="preserve">CFTS084-134738
+CFTS084-134739
+CFTS084-134740
+CFTS084-134744
+CFTS084-134751
+CFTS084-134752
+CFTS084-134753
+CFTS084-134755
+CFTS084-134756
+CFTS084-134757
+CFTS084-134758
+CFTS084-134759
+CFTS084-134760
+CFTS084-134761
+CFTS084-134762
+CFTS084-134844
+CFTS084-134845
+CFTS084-134847</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8352,7 +8373,24 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUONLINE</t>
+          <t xml:space="preserve">CFTS084-134738
+CFTS084-134739
+CFTS084-134740
+CFTS084-134744
+CFTS084-134751
+CFTS084-134752
+CFTS084-134753
+CFTS084-134755
+CFTS084-134756
+CFTS084-134757
+CFTS084-134758
+CFTS084-134759
+CFTS084-134760
+CFTS084-134761
+CFTS084-134762
+CFTS084-134844
+CFTS084-134845
+CFTS084-134847</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8490,7 +8528,13 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUCERT_SERVICE_BINDER</t>
+          <t xml:space="preserve">CFTS084-134739
+CFTS084-134744
+CFTS084-134751
+CFTS084-134752
+CFTS084-134754
+CFTS084-134844
+CFTS084-134845</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8628,7 +8672,12 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUONLINE_BINDER</t>
+          <t xml:space="preserve">CFTS084-134739
+CFTS084-134744
+CFTS084-134751
+CFTS084-134752
+CFTS084-134844
+CFTS084-134845</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8766,7 +8815,13 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUCERT_STORAGE_IO</t>
+          <t xml:space="preserve">CFTS084-134739
+CFTS084-134744
+CFTS084-134751
+CFTS084-134752
+CFTS084-134754
+CFTS084-134844
+CFTS084-134845</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8904,7 +8959,13 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUCERT_JNI</t>
+          <t xml:space="preserve">CFTS084-134739
+CFTS084-134744
+CFTS084-134751
+CFTS084-134752
+CFTS084-134754
+CFTS084-134844
+CFTS084-134845</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9042,7 +9103,30 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUONLINE_DOWNLOADCERT_INTF</t>
+          <t xml:space="preserve">CFTS084-134739
+CFTS084-134741
+CFTS084-134742
+CFTS084-134743
+CFTS084-134744
+CFTS084-134745
+CFTS084-134746
+CFTS084-134747
+CFTS084-134748
+CFTS084-134749
+CFTS084-134750
+CFTS084-134751
+CFTS084-134752
+CFTS084-134753
+CFTS084-134755
+CFTS084-134756
+CFTS084-134757
+CFTS084-134758
+CFTS084-134759
+CFTS084-134761
+CFTS084-134762
+CFTS084-134844
+CFTS084-134845
+CFTS084-134847</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9180,7 +9264,30 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_ECUCert_FM-WI-FSM-037-A03_SYSAD_SEC_ECUCERT_ECUONLINE_DOWNLOADCERT_INTF</t>
+          <t xml:space="preserve">CFTS084-134739
+CFTS084-134741
+CFTS084-134742
+CFTS084-134743
+CFTS084-134744
+CFTS084-134745
+CFTS084-134746
+CFTS084-134747
+CFTS084-134748
+CFTS084-134749
+CFTS084-134750
+CFTS084-134751
+CFTS084-134752
+CFTS084-134753
+CFTS084-134755
+CFTS084-134756
+CFTS084-134757
+CFTS084-134758
+CFTS084-134759
+CFTS084-134761
+CFTS084-134762
+CFTS084-134844
+CFTS084-134845
+CFTS084-134847</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9318,7 +9425,70 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-001</t>
+          <t xml:space="preserve">CFTS084-134520
+CFTS084-134521
+CFTS084-134522
+CFTS084-134523
+CFTS084-134524
+CFTS084-134525
+CFTS084-134526
+CFTS084-134529
+CFTS084-134531
+CFTS084-134532
+CFTS084-134533
+CFTS084-134534
+CFTS084-134535
+CFTS084-134536
+CFTS084-134537
+CFTS084-134538
+CFTS084-134539
+CFTS084-134541
+CFTS084-134542
+CFTS084-134543
+CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134584
+CFTS084-134585
+CFTS084-134586
+CFTS084-134587
+CFTS084-134588
+CFTS084-134589
+CFTS084-134590
+CFTS084-134591
+CFTS084-134592
+CFTS084-134593
+CFTS084-134595
+CFTS084-134596
+CFTS084-134597
+CFTS084-134598
+CFTS084-134599
+CFTS084-134600
+CFTS084-134601
+CFTS084-134602
+CFTS084-134603
+CFTS084-134604
+CFTS084-134605
+CFTS084-134607
+CFTS084-134608
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613
+CFTS084-134804
+CFTS084-134823
+CFTS084-134824
+CFTS084-134825
+CFTS084-134827
+CFTS084-134828
+CFTS084-134841
+CFTS084-134849</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9456,7 +9626,70 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-001</t>
+          <t xml:space="preserve">CFTS084-134520
+CFTS084-134521
+CFTS084-134522
+CFTS084-134523
+CFTS084-134524
+CFTS084-134525
+CFTS084-134526
+CFTS084-134529
+CFTS084-134531
+CFTS084-134532
+CFTS084-134533
+CFTS084-134534
+CFTS084-134535
+CFTS084-134536
+CFTS084-134537
+CFTS084-134538
+CFTS084-134539
+CFTS084-134541
+CFTS084-134542
+CFTS084-134543
+CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134584
+CFTS084-134585
+CFTS084-134586
+CFTS084-134587
+CFTS084-134588
+CFTS084-134589
+CFTS084-134590
+CFTS084-134591
+CFTS084-134592
+CFTS084-134593
+CFTS084-134595
+CFTS084-134596
+CFTS084-134597
+CFTS084-134598
+CFTS084-134599
+CFTS084-134600
+CFTS084-134601
+CFTS084-134602
+CFTS084-134603
+CFTS084-134604
+CFTS084-134605
+CFTS084-134607
+CFTS084-134608
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613
+CFTS084-134804
+CFTS084-134823
+CFTS084-134824
+CFTS084-134825
+CFTS084-134827
+CFTS084-134828
+CFTS084-134841
+CFTS084-134849</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9594,7 +9827,16 @@
       </c>
       <c r="N22" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-002</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O22" s="81" t="inlineStr">
@@ -9732,7 +9974,16 @@
       </c>
       <c r="N23" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-005</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O23" s="81" t="inlineStr">
@@ -9870,7 +10121,16 @@
       </c>
       <c r="N24" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-005</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O24" s="81" t="inlineStr">
@@ -10008,7 +10268,7 @@
       </c>
       <c r="N25" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-001</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O25" s="81" t="inlineStr">
@@ -10145,7 +10405,7 @@
       </c>
       <c r="N26" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-002</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O26" s="81" t="inlineStr">
@@ -10282,7 +10542,7 @@
       </c>
       <c r="N27" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-003</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O27" s="81" t="inlineStr">
@@ -10419,7 +10679,7 @@
       </c>
       <c r="N28" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-004</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O28" s="81" t="inlineStr">
@@ -10557,7 +10817,7 @@
       </c>
       <c r="N29" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-004</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O29" s="81" t="inlineStr">
@@ -10695,7 +10955,7 @@
       </c>
       <c r="N30" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-005</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O30" s="81" t="inlineStr">
@@ -10832,7 +11092,7 @@
       </c>
       <c r="N31" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-007</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O31" s="81" t="inlineStr">
@@ -10969,7 +11229,7 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-008</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11106,7 +11366,7 @@
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_libLogEncrypt_FM-WI-FSM-037-A03_SWE1-LOGENC-009</t>
+          <t xml:space="preserve">CFTS084-134686</t>
         </is>
       </c>
       <c r="O33" s="81" t="inlineStr">

--- a/features/security/sandbox/batch3/security_batch3_v01.xlsx
+++ b/features/security/sandbox/batch3/security_batch3_v01.xlsx
@@ -7940,9 +7940,9 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8079,9 +8079,9 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8218,24 +8218,24 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134738
-CFTS084-134739
-CFTS084-134740
-CFTS084-134744
-CFTS084-134751
-CFTS084-134752
-CFTS084-134753
-CFTS084-134755
-CFTS084-134756
-CFTS084-134757
-CFTS084-134758
-CFTS084-134759
-CFTS084-134760
-CFTS084-134761
-CFTS084-134762
-CFTS084-134844
-CFTS084-134845
-CFTS084-134847</t>
+          <t xml:space="preserve">CFTS084-4949786
+CFTS084-4949787
+CFTS084-4949788
+CFTS084-4949792
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949801
+CFTS084-4949803
+CFTS084-4949804
+CFTS084-4949805
+CFTS084-4949806
+CFTS084-4949807
+CFTS084-4949808
+CFTS084-4949809
+CFTS084-4949810
+CFTS084-4949900
+CFTS084-4949901
+CFTS084-4949903</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8373,24 +8373,24 @@
       </c>
       <c r="N13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134738
-CFTS084-134739
-CFTS084-134740
-CFTS084-134744
-CFTS084-134751
-CFTS084-134752
-CFTS084-134753
-CFTS084-134755
-CFTS084-134756
-CFTS084-134757
-CFTS084-134758
-CFTS084-134759
-CFTS084-134760
-CFTS084-134761
-CFTS084-134762
-CFTS084-134844
-CFTS084-134845
-CFTS084-134847</t>
+          <t xml:space="preserve">CFTS084-4949786
+CFTS084-4949787
+CFTS084-4949788
+CFTS084-4949792
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949801
+CFTS084-4949803
+CFTS084-4949804
+CFTS084-4949805
+CFTS084-4949806
+CFTS084-4949807
+CFTS084-4949808
+CFTS084-4949809
+CFTS084-4949810
+CFTS084-4949900
+CFTS084-4949901
+CFTS084-4949903</t>
         </is>
       </c>
       <c r="O13" s="81" t="inlineStr">
@@ -8528,13 +8528,13 @@
       </c>
       <c r="N14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134739
-CFTS084-134744
-CFTS084-134751
-CFTS084-134752
-CFTS084-134754
-CFTS084-134844
-CFTS084-134845</t>
+          <t xml:space="preserve">CFTS084-4949787
+CFTS084-4949792
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949802
+CFTS084-4949900
+CFTS084-4949901</t>
         </is>
       </c>
       <c r="O14" s="81" t="inlineStr">
@@ -8672,12 +8672,12 @@
       </c>
       <c r="N15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134739
-CFTS084-134744
-CFTS084-134751
-CFTS084-134752
-CFTS084-134844
-CFTS084-134845</t>
+          <t xml:space="preserve">CFTS084-4949787
+CFTS084-4949792
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949900
+CFTS084-4949901</t>
         </is>
       </c>
       <c r="O15" s="81" t="inlineStr">
@@ -8815,13 +8815,13 @@
       </c>
       <c r="N16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134739
-CFTS084-134744
-CFTS084-134751
-CFTS084-134752
-CFTS084-134754
-CFTS084-134844
-CFTS084-134845</t>
+          <t xml:space="preserve">CFTS084-4949787
+CFTS084-4949792
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949802
+CFTS084-4949900
+CFTS084-4949901</t>
         </is>
       </c>
       <c r="O16" s="81" t="inlineStr">
@@ -8959,13 +8959,13 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134739
-CFTS084-134744
-CFTS084-134751
-CFTS084-134752
-CFTS084-134754
-CFTS084-134844
-CFTS084-134845</t>
+          <t xml:space="preserve">CFTS084-4949787
+CFTS084-4949792
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949802
+CFTS084-4949900
+CFTS084-4949901</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9103,30 +9103,30 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134739
-CFTS084-134741
-CFTS084-134742
-CFTS084-134743
-CFTS084-134744
-CFTS084-134745
-CFTS084-134746
-CFTS084-134747
-CFTS084-134748
-CFTS084-134749
-CFTS084-134750
-CFTS084-134751
-CFTS084-134752
-CFTS084-134753
-CFTS084-134755
-CFTS084-134756
-CFTS084-134757
-CFTS084-134758
-CFTS084-134759
-CFTS084-134761
-CFTS084-134762
-CFTS084-134844
-CFTS084-134845
-CFTS084-134847</t>
+          <t xml:space="preserve">CFTS084-4949787
+CFTS084-4949789
+CFTS084-4949790
+CFTS084-4949791
+CFTS084-4949792
+CFTS084-4949793
+CFTS084-4949794
+CFTS084-4949795
+CFTS084-4949796
+CFTS084-4949797
+CFTS084-4949798
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949801
+CFTS084-4949803
+CFTS084-4949804
+CFTS084-4949805
+CFTS084-4949806
+CFTS084-4949807
+CFTS084-4949809
+CFTS084-4949810
+CFTS084-4949900
+CFTS084-4949901
+CFTS084-4949903</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9264,30 +9264,30 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134739
-CFTS084-134741
-CFTS084-134742
-CFTS084-134743
-CFTS084-134744
-CFTS084-134745
-CFTS084-134746
-CFTS084-134747
-CFTS084-134748
-CFTS084-134749
-CFTS084-134750
-CFTS084-134751
-CFTS084-134752
-CFTS084-134753
-CFTS084-134755
-CFTS084-134756
-CFTS084-134757
-CFTS084-134758
-CFTS084-134759
-CFTS084-134761
-CFTS084-134762
-CFTS084-134844
-CFTS084-134845
-CFTS084-134847</t>
+          <t xml:space="preserve">CFTS084-4949787
+CFTS084-4949789
+CFTS084-4949790
+CFTS084-4949791
+CFTS084-4949792
+CFTS084-4949793
+CFTS084-4949794
+CFTS084-4949795
+CFTS084-4949796
+CFTS084-4949797
+CFTS084-4949798
+CFTS084-4949799
+CFTS084-4949800
+CFTS084-4949801
+CFTS084-4949803
+CFTS084-4949804
+CFTS084-4949805
+CFTS084-4949806
+CFTS084-4949807
+CFTS084-4949809
+CFTS084-4949810
+CFTS084-4949900
+CFTS084-4949901
+CFTS084-4949903</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9425,70 +9425,70 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134520
-CFTS084-134521
-CFTS084-134522
-CFTS084-134523
-CFTS084-134524
-CFTS084-134525
-CFTS084-134526
-CFTS084-134529
-CFTS084-134531
-CFTS084-134532
-CFTS084-134533
-CFTS084-134534
-CFTS084-134535
-CFTS084-134536
-CFTS084-134537
-CFTS084-134538
-CFTS084-134539
-CFTS084-134541
-CFTS084-134542
-CFTS084-134543
-CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134584
-CFTS084-134585
-CFTS084-134586
-CFTS084-134587
-CFTS084-134588
-CFTS084-134589
-CFTS084-134590
-CFTS084-134591
-CFTS084-134592
-CFTS084-134593
-CFTS084-134595
-CFTS084-134596
-CFTS084-134597
-CFTS084-134598
-CFTS084-134599
-CFTS084-134600
-CFTS084-134601
-CFTS084-134602
-CFTS084-134603
-CFTS084-134604
-CFTS084-134605
-CFTS084-134607
-CFTS084-134608
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613
-CFTS084-134804
-CFTS084-134823
-CFTS084-134824
-CFTS084-134825
-CFTS084-134827
-CFTS084-134828
-CFTS084-134841
-CFTS084-134849</t>
+          <t xml:space="preserve">CFTS084-4949510
+CFTS084-4949511
+CFTS084-4949512
+CFTS084-4949513
+CFTS084-4949516
+CFTS084-4949521
+CFTS084-4949522
+CFTS084-4949529
+CFTS084-4949531
+CFTS084-4949532
+CFTS084-4949533
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949538
+CFTS084-4949540
+CFTS084-4949541
+CFTS084-4949542
+CFTS084-4949545
+CFTS084-4949546
+CFTS084-4949547
+CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949614
+CFTS084-4949615
+CFTS084-4949617
+CFTS084-4949618
+CFTS084-4949619
+CFTS084-4949620
+CFTS084-4949621
+CFTS084-4949622
+CFTS084-4949623
+CFTS084-4949624
+CFTS084-4949627
+CFTS084-4949628
+CFTS084-4949629
+CFTS084-4949630
+CFTS084-4949631
+CFTS084-4949632
+CFTS084-4949633
+CFTS084-4949634
+CFTS084-4949635
+CFTS084-4949636
+CFTS084-4949637
+CFTS084-4949639
+CFTS084-4949640
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646
+CFTS084-4949853
+CFTS084-4949878
+CFTS084-4949879
+CFTS084-4949880
+CFTS084-4949882
+CFTS084-4949883
+CFTS084-4949896
+CFTS084-4949905</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
@@ -9626,70 +9626,70 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134520
-CFTS084-134521
-CFTS084-134522
-CFTS084-134523
-CFTS084-134524
-CFTS084-134525
-CFTS084-134526
-CFTS084-134529
-CFTS084-134531
-CFTS084-134532
-CFTS084-134533
-CFTS084-134534
-CFTS084-134535
-CFTS084-134536
-CFTS084-134537
-CFTS084-134538
-CFTS084-134539
-CFTS084-134541
-CFTS084-134542
-CFTS084-134543
-CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134584
-CFTS084-134585
-CFTS084-134586
-CFTS084-134587
-CFTS084-134588
-CFTS084-134589
-CFTS084-134590
-CFTS084-134591
-CFTS084-134592
-CFTS084-134593
-CFTS084-134595
-CFTS084-134596
-CFTS084-134597
-CFTS084-134598
-CFTS084-134599
-CFTS084-134600
-CFTS084-134601
-CFTS084-134602
-CFTS084-134603
-CFTS084-134604
-CFTS084-134605
-CFTS084-134607
-CFTS084-134608
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613
-CFTS084-134804
-CFTS084-134823
-CFTS084-134824
-CFTS084-134825
-CFTS084-134827
-CFTS084-134828
-CFTS084-134841
-CFTS084-134849</t>
+          <t xml:space="preserve">CFTS084-4949510
+CFTS084-4949511
+CFTS084-4949512
+CFTS084-4949513
+CFTS084-4949516
+CFTS084-4949521
+CFTS084-4949522
+CFTS084-4949529
+CFTS084-4949531
+CFTS084-4949532
+CFTS084-4949533
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949538
+CFTS084-4949540
+CFTS084-4949541
+CFTS084-4949542
+CFTS084-4949545
+CFTS084-4949546
+CFTS084-4949547
+CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949614
+CFTS084-4949615
+CFTS084-4949617
+CFTS084-4949618
+CFTS084-4949619
+CFTS084-4949620
+CFTS084-4949621
+CFTS084-4949622
+CFTS084-4949623
+CFTS084-4949624
+CFTS084-4949627
+CFTS084-4949628
+CFTS084-4949629
+CFTS084-4949630
+CFTS084-4949631
+CFTS084-4949632
+CFTS084-4949633
+CFTS084-4949634
+CFTS084-4949635
+CFTS084-4949636
+CFTS084-4949637
+CFTS084-4949639
+CFTS084-4949640
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646
+CFTS084-4949853
+CFTS084-4949878
+CFTS084-4949879
+CFTS084-4949880
+CFTS084-4949882
+CFTS084-4949883
+CFTS084-4949896
+CFTS084-4949905</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9827,16 +9827,16 @@
       </c>
       <c r="N22" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O22" s="81" t="inlineStr">
@@ -9974,16 +9974,16 @@
       </c>
       <c r="N23" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O23" s="81" t="inlineStr">
@@ -10121,16 +10121,16 @@
       </c>
       <c r="N24" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O24" s="81" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="N25" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O25" s="81" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="N26" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O26" s="81" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="N27" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O27" s="81" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="N28" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O28" s="81" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="N29" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O29" s="81" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="N30" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O30" s="81" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="N31" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O31" s="81" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="N33" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134686</t>
+          <t xml:space="preserve">CFTS084-4949731</t>
         </is>
       </c>
       <c r="O33" s="81" t="inlineStr">

--- a/features/security/sandbox/batch3/security_batch3_v01.xlsx
+++ b/features/security/sandbox/batch3/security_batch3_v01.xlsx
@@ -8175,7 +8175,7 @@
       <c r="E12" s="81"/>
       <c r="F12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-013</t>
+          <t xml:space="preserve">NR1L-ECUC-018</t>
         </is>
       </c>
       <c r="G12" s="81" t="inlineStr">
@@ -8330,7 +8330,7 @@
       <c r="E13" s="81"/>
       <c r="F13" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-014</t>
+          <t xml:space="preserve">NR1L-ECUC-019</t>
         </is>
       </c>
       <c r="G13" s="81" t="inlineStr">
@@ -8485,7 +8485,7 @@
       <c r="E14" s="81"/>
       <c r="F14" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-015</t>
+          <t xml:space="preserve">NR1L-ECUC-020</t>
         </is>
       </c>
       <c r="G14" s="81" t="inlineStr">
@@ -8629,7 +8629,7 @@
       <c r="E15" s="81"/>
       <c r="F15" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-016</t>
+          <t xml:space="preserve">NR1L-ECUC-021</t>
         </is>
       </c>
       <c r="G15" s="81" t="inlineStr">
@@ -8772,7 +8772,7 @@
       <c r="E16" s="81"/>
       <c r="F16" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-017</t>
+          <t xml:space="preserve">NR1L-ECUC-022</t>
         </is>
       </c>
       <c r="G16" s="81" t="inlineStr">
@@ -8916,7 +8916,7 @@
       <c r="E17" s="81"/>
       <c r="F17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-018</t>
+          <t xml:space="preserve">NR1L-ECUC-023</t>
         </is>
       </c>
       <c r="G17" s="81" t="inlineStr">
@@ -9060,7 +9060,7 @@
       <c r="E18" s="81"/>
       <c r="F18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-019</t>
+          <t xml:space="preserve">NR1L-ECUC-024</t>
         </is>
       </c>
       <c r="G18" s="81" t="inlineStr">
@@ -9221,7 +9221,7 @@
       <c r="E19" s="81"/>
       <c r="F19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">NR1L-ECUC-020</t>
+          <t xml:space="preserve">NR1L-ECUC-025</t>
         </is>
       </c>
       <c r="G19" s="81" t="inlineStr">
